--- a/services/agent/app/static/sample/telop-manuscript.xlsx
+++ b/services/agent/app/static/sample/telop-manuscript.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Source: webapps.dol.gov</t>
+          <t>Source: www.dol.gov</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Source: dol.georgia.gov</t>
+          <t>Source: www.dol.gov</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">

--- a/services/agent/app/static/sample/telop-manuscript.xlsx
+++ b/services/agent/app/static/sample/telop-manuscript.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="テロップ原稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Caption Order Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'テロップ原稿'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Caption Order Sheet'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
     </font>
     <font>
       <color rgb="008A5A12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0096311F"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +103,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,40 +473,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>テロップ原稿</t>
+          <t>Caption Order Sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>番組・企画: The corner coffee shop against convenience-store coffee (Quick Judge Demo)</t>
+          <t>Programme: The corner coffee shop against convenience-store coffee (Quick Judge Demo)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OA:</t>
+          <t>Air date: 2026-08-07</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>※「裏付け」欄が⚠または裏付けなしの行は、数字を出す前に確認してください</t>
+          <t>Rows marked ⚠ or 'not backed' in Checked against: confirm the figure before it goes to air.</t>
         </is>
       </c>
     </row>
@@ -511,37 +518,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>IN点</t>
+          <t>In</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>OUT点</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>表示文字</t>
+          <t>On screen</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>出典表記</t>
+          <t>Source line</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>裏付け</t>
+          <t>Checked against</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>備考・確認事項</t>
+          <t>Notes / to confirm</t>
         </is>
       </c>
     </row>
@@ -561,19 +568,19 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>場所スーパー</t>
+          <t>location super</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Old brick buildings, street
-Coffee shop, sunset glow</t>
+          <t>Sunset over quiet street,
+Old brick bldgs &amp; storefront</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
@@ -584,28 +591,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>00:00:14:22</t>
+          <t>00:00:15:04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>00:00:18:04</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>名前スーパー</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Male Barista</t>
+          <t>Cafe Owner</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -620,105 +627,105 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>00:00:14:22</t>
+          <t>00:00:15:04</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>00:00:18:04</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Opened by my father,
-1978</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>裏付けなし</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+          <t>Federal minimum wage,
+$7.25 an hour</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Source: labour.gov.example</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>multiple sources</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>00:00:14:22</t>
+          <t>00:00:15:04</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>00:00:18:04</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Father opened this in 1978</t>
+          <t>Business pays fed min wage
+$7.25 an hour</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>00:00:18:04</t>
+          <t>00:00:15:04</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>00:00:21:14</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>male barista: 22 years
-behind this counter</t>
+          <t>We pay the federal minimum wage</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>裏付けなし</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
-        </is>
-      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -726,31 +733,35 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>00:00:18:04</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>00:00:21:14</t>
+          <t>00:00:17:07</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Behind this counter for 22 years</t>
+          <t>Interviewer</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the spelling of the name and title with the speaker.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -758,35 +769,31 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>00:00:21:14</t>
+          <t>00:00:17:01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>00:00:26:14</t>
+          <t>00:00:17:07</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>名前スーパー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>Mhm</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Confirm the spelling of the name and title with the speaker.</t>
-        </is>
-      </c>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -794,70 +801,65 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>00:00:21:14</t>
+          <t>00:00:17:07</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:14</t>
+          <t>00:00:19:07</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Small businesses employ almost
-half the private workforce</t>
+          <t>Federal minimum wage
+Unchanged since 2009</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Source: advocacy.sba.gov</t>
+          <t>Source: labour.gov.example</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>複数ソースで確認</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Frequently Asked Questions About Small Business 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+          <t>multiple sources</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>00:00:21:14</t>
+          <t>00:00:17:07</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:14</t>
+          <t>00:00:19:07</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Small businesses employ
-almost half of private workforce</t>
+          <t>Hasn't changed since 2009</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -868,35 +870,31 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:14</t>
+          <t>00:00:19:07</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>00:00:30:14</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>名前スーパー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Man in apron</t>
+          <t>mhm</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Confirm the spelling of the name and title with the speaker.</t>
-        </is>
-      </c>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -904,96 +902,102 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:14</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>00:00:30:14</t>
+          <t>00:00:23:27</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>federal minimum wage $7.25/hr</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Source: www.dol.gov</t>
-        </is>
-      </c>
+          <t>Man in apron</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>複数ソースで確認</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the spelling of the name and title with the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:14</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>00:00:30:14</t>
+          <t>00:00:23:27</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Federal minimum wage paid here</t>
+          <t>Over 150,000 convenience stores
+in the country</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
+          <t>multiple sources</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Checked, but no primary source to credit (backed by retailcouncil.example, forecourt.example). Find the official release before adding a source line.／as of 31 December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>00:00:30:14</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:20</t>
+          <t>00:00:23:27</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>$7.25 an hour</t>
+          <t>Over 150,000 convenience
+stores in this country</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr"/>
@@ -1004,38 +1008,34 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:20</t>
+          <t>00:00:23:27</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>00:00:35:02</t>
+          <t>00:00:25:25</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Federal minimum wage
-$7.25/hr, unchanged since 2009</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Source: www.dol.gov</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>複数ソースで確認</t>
+          <t>Nearly all convenience stores
+sell coffee</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>⚠ conflicts with published figures</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>December 31, 2013</t>
+          <t>Do not use this figure as spoken — it conflicts with published data.</t>
         </is>
       </c>
     </row>
@@ -1045,66 +1045,65 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:20</t>
+          <t>00:00:23:27</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>00:00:35:02</t>
+          <t>00:00:25:25</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>It hasn't changed since 2009</t>
+          <t>Nearly all of them sell coffee</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>00:00:35:02</t>
+          <t>00:00:25:25</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:02</t>
+          <t>00:00:28:29</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Over 150,000 convenience
-stores in this country</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>複数ソースで確認</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Checked, but no primary source to credit (backed by www.convenience.org, csnews.com). Find the official release before adding a source line.／as of Dec. 31, 2025</t>
+          <t>Confirm the spelling of the name and title with the speaker.</t>
         </is>
       </c>
     </row>
@@ -1114,69 +1113,68 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>00:00:35:02</t>
+          <t>00:00:25:25</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:02</t>
+          <t>00:00:28:29</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Over 150,000 convenience
-stores in this country</t>
+          <t>Store sells 200 cups coffee
+daily</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:02</t>
+          <t>00:00:25:25</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>00:00:41:22</t>
+          <t>00:00:28:29</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Nearly all convenience stores
-sell coffee nationwide</t>
+          <t>We do about 200 cups a day</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>裏付けなし</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Nothing backs this. Attribute it to the speaker, or drop the number.</t>
-        </is>
-      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -1184,60 +1182,61 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:02</t>
+          <t>00:00:28:29</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>00:00:41:22</t>
+          <t>00:00:29:10</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Nearly all sell coffee</t>
+          <t>Yeah</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>00:00:41:22</t>
+          <t>00:00:29:10</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>00:00:44:22</t>
+          <t>00:00:32:11</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>200 cups of coffee daily</t>
+          <t>10 years ago, sold ~300
+coffee/day</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>裏付けなし</t>
+          <t>not backed</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1252,68 +1251,63 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>00:00:41:22</t>
+          <t>00:00:29:10</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>00:00:44:22</t>
+          <t>00:00:32:11</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>About 200 cups a day</t>
+          <t>10 years ago, closer to 300</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>00:00:44:22</t>
+          <t>00:00:32:11</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>00:00:47:22</t>
+          <t>00:00:32:20</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>10 years ago, daily coffee
-sales were ~300 cups</t>
+          <t>Yeah</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>裏付けなし</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -1321,66 +1315,67 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>00:00:44:22</t>
+          <t>00:00:32:20</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>00:00:47:22</t>
+          <t>00:00:36:23</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>10 years ago, it was closer to
-300</t>
+          <t>You can taste the difference,
+when made by hand</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>00:00:47:22</t>
+          <t>00:00:36:23</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>00:00:52:08</t>
+          <t>00:00:39:26</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>名前スーパー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Elderly woman</t>
+          <t>Many shops on this street
+have closed</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>素材どおり</t>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Confirm the spelling of the name and title with the speaker.</t>
+          <t>No named subject — cannot be checked. Attribute it to the speaker.</t>
         </is>
       </c>
     </row>
@@ -1390,67 +1385,66 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>00:00:47:22</t>
+          <t>00:00:36:23</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>00:00:52:08</t>
+          <t>00:00:39:26</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>You can taste the difference
-when made by hand</t>
+          <t>Many shops along this street
+have closed down</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>00:00:52:08</t>
+          <t>00:00:39:26</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:15</t>
+          <t>00:00:42:26</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>データテロップ</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Many shops along this street
-have closed</t>
+          <t>Barista</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>裏付けなし</t>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>No named subject — cannot be checked. Attribute it to the speaker.</t>
+          <t>Confirm the spelling of the name and title with the speaker.</t>
         </is>
       </c>
     </row>
@@ -1460,32 +1454,36 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>00:00:52:08</t>
+          <t>00:00:39:26</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:15</t>
+          <t>00:00:42:26</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Many shops along this street
-have closed</t>
+          <t>the barista's business
+opened in 1978</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1493,35 +1491,31 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:15</t>
+          <t>00:00:39:26</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:24</t>
+          <t>00:00:42:26</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>名前スーパー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Off-screen interviewer</t>
+          <t>my father opened in 1978</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Confirm the spelling of the name and title with the speaker.</t>
-        </is>
-      </c>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -1529,95 +1523,142 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:15</t>
+          <t>00:00:42:26</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:24</t>
+          <t>00:00:46:03</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>yeah</t>
+          <t>22 years behind counter</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>00:00:55:24</t>
+          <t>00:00:42:26</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>00:00:56:03</t>
+          <t>00:00:46:03</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Yeah</t>
+          <t>Behind this counter,
+for 22 years</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>00:00:56:03</t>
+          <t>00:00:46:03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>00:00:56:15</t>
+          <t>00:00:53:00</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>コメントフォロー</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Mhm</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr"/>
+          <t>Small businesses employ
+almost half of private workforce</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Source: smallbiz.gov.example</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>素材どおり</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
+          <t>multiple sources</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>current as of 31 December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>00:00:46:03</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>00:00:53:00</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>quote follow</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Small businesses employ almost
+half of private workforce</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/agent/app/static/sample/telop-manuscript.xlsx
+++ b/services/agent/app/static/sample/telop-manuscript.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -573,8 +573,8 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Sunset over quiet street,
-Old brick bldgs &amp; storefront</t>
+          <t>Sunset on quiet street, bricks
+Storefront glow, street light</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Federal minimum wage,
+          <t>Federal minimum wage
 $7.25 an hour</t>
         </is>
       </c>
@@ -679,21 +679,21 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Business pays fed min wage
-$7.25 an hour</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>not backed</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
-        </is>
-      </c>
+          <t>Federal minimum wage
+unchanged since 2009</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Source: labour.gov.example</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>multiple sources</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>We pay the federal minimum wage</t>
+          <t>Federal minimum wage paid</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>00:00:17:07</t>
+          <t>00:00:17:16</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>00:00:17:07</t>
+          <t>00:00:17:16</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>00:00:17:07</t>
+          <t>00:00:17:16</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:07</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -816,8 +816,8 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Federal minimum wage
-Unchanged since 2009</t>
+          <t>Federal minimum wage unchanged
+since 2009</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>00:00:17:07</t>
+          <t>00:00:17:16</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:07</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Hasn't changed since 2009</t>
+          <t>It hasn't changed since 2009</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:07</t>
+          <t>00:00:19:16</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:16</t>
+          <t>00:00:19:25</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>mhm</t>
+          <t>Mhm</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -902,12 +902,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:16</t>
+          <t>00:00:19:25</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>00:00:23:27</t>
+          <t>00:00:22:28</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Man in apron</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:16</t>
+          <t>00:00:19:25</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>00:00:23:27</t>
+          <t>00:00:22:28</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -953,34 +953,34 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Over 150,000 convenience stores
-in the country</t>
+          <t>Sells about 200 cups coffee
+a day</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>multiple sources</t>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Checked, but no primary source to credit (backed by retailcouncil.example, forecourt.example). Find the official release before adding a source line.／as of 31 December 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>00:00:19:16</t>
+          <t>00:00:19:25</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>00:00:23:27</t>
+          <t>00:00:22:28</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -990,8 +990,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Over 150,000 convenience
-stores in this country</t>
+          <t>200 cups a day</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -1002,42 +1001,37 @@
       </c>
       <c r="H17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>00:00:23:27</t>
+          <t>00:00:22:28</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>00:00:25:25</t>
+          <t>00:00:23:09</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>data caption</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Nearly all convenience stores
-sell coffee</t>
+          <t>Yeah</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>⚠ conflicts with published figures</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Do not use this figure as spoken — it conflicts with published data.</t>
-        </is>
-      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -1045,12 +1039,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>00:00:23:27</t>
+          <t>00:00:23:09</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>00:00:25:25</t>
+          <t>00:00:23:18</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1060,7 +1054,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Nearly all of them sell coffee</t>
+          <t>yeah</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -1077,12 +1071,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>00:00:25:25</t>
+          <t>00:00:23:18</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:29</t>
+          <t>00:00:27:29</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1092,7 +1086,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>Man in apron</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -1113,12 +1107,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>00:00:25:25</t>
+          <t>00:00:23:18</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:29</t>
+          <t>00:00:27:29</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1128,19 +1122,19 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Store sells 200 cups coffee
-daily</t>
+          <t>Convenience stores
+Over 150,000 in this country</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>not backed</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>multiple sources</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+          <t>Checked, but no primary source to credit (backed by retailcouncil.example, forecourt.example). Find the official release before adding a source line.／as of 31 December 2025</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1144,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>00:00:25:25</t>
+          <t>00:00:23:18</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:29</t>
+          <t>00:00:27:29</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1165,7 +1159,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>We do about 200 cups a day</t>
+          <t>Over 150,000 stores nationwide</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
@@ -1176,87 +1170,87 @@
       </c>
       <c r="H22" s="6" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>00:00:28:29</t>
+          <t>00:00:27:29</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>00:00:29:10</t>
+          <t>00:00:29:27</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>quote follow</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Yeah</t>
+          <t>nearly all convenience stores
+sell coffee</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>as recorded</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>⚠ conflicts with published figures</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Do not use this figure as spoken — it conflicts with published data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>00:00:29:10</t>
+          <t>00:00:27:29</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:11</t>
+          <t>00:00:29:27</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>data caption</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>10 years ago, sold ~300
-coffee/day</t>
+          <t>Nearly all of them sell coffee</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>not backed</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>00:00:29:10</t>
+          <t>00:00:29:27</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:11</t>
+          <t>00:00:34:00</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1266,7 +1260,8 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>10 years ago, closer to 300</t>
+          <t>Taste the difference
+when made by hand</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
@@ -1283,31 +1278,35 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:11</t>
+          <t>00:00:34:00</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:20</t>
+          <t>00:00:37:03</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>quote follow</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Yeah</t>
+          <t>Many shops on this street closed</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>as recorded</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>No named subject — cannot be checked. Attribute it to the speaker.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -1315,12 +1314,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>00:00:32:20</t>
+          <t>00:00:34:00</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>00:00:36:23</t>
+          <t>00:00:37:03</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1330,8 +1329,8 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>You can taste the difference,
-when made by hand</t>
+          <t>Many shops along this street,
+have closed</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr"/>
@@ -1342,98 +1341,101 @@
       </c>
       <c r="H27" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>00:00:36:23</t>
+          <t>00:00:37:03</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:26</t>
+          <t>00:00:40:03</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>data caption</t>
+          <t>name super</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Many shops on this street
-have closed</t>
+          <t>Barista</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>not backed</t>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>as recorded</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No named subject — cannot be checked. Attribute it to the speaker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>Confirm the spelling of the name and title with the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>00:00:36:23</t>
+          <t>00:00:37:03</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:26</t>
+          <t>00:00:40:03</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>quote follow</t>
+          <t>data caption</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Many shops along this street
-have closed down</t>
+          <t>Business opened in 1978</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>as recorded</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>not backed</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>No named subject — cannot be checked. Attribute it to the speaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:26</t>
+          <t>00:00:37:03</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>00:00:42:26</t>
+          <t>00:00:40:03</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>name super</t>
+          <t>quote follow</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Barista</t>
+          <t>My father opened this place,
+in 1978</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr"/>
@@ -1442,24 +1444,20 @@
           <t>as recorded</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Confirm the spelling of the name and title with the speaker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:26</t>
+          <t>00:00:40:03</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>00:00:42:26</t>
+          <t>00:00:43:11</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1469,8 +1467,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>the barista's business
-opened in 1978</t>
+          <t>Barista behind counter 22 years</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr"/>
@@ -1491,12 +1488,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>00:00:39:26</t>
+          <t>00:00:40:03</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>00:00:42:26</t>
+          <t>00:00:43:11</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1506,7 +1503,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>my father opened in 1978</t>
+          <t>Behind this counter for 22 years</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
@@ -1517,18 +1514,18 @@
       </c>
       <c r="H32" s="6" t="inlineStr"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>00:00:42:26</t>
+          <t>00:00:43:11</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>00:00:46:03</t>
+          <t>00:00:50:08</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1538,18 +1535,23 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>22 years behind counter</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>not backed</t>
+          <t>Small businesses employ almost
+half of private workforce</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Source: smallbiz.gov.example</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>multiple sources</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Their own figure — nobody publishes it. Attribute it to the speaker.</t>
+          <t>current as of 31 December 2025</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1561,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>00:00:42:26</t>
+          <t>00:00:43:11</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>00:00:46:03</t>
+          <t>00:00:50:08</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1574,8 +1576,8 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Behind this counter,
-for 22 years</t>
+          <t>Small businesses employ
+almost half private workforce</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1585,80 +1587,6 @@
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>00:00:46:03</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>00:00:53:00</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>data caption</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Small businesses employ
-almost half of private workforce</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>Source: smallbiz.gov.example</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>multiple sources</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>current as of 31 December 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>00:00:46:03</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>00:00:53:00</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>quote follow</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Small businesses employ almost
-half of private workforce</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>as recorded</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
